--- a/data/books.xlsx
+++ b/data/books.xlsx
@@ -7,16 +7,14 @@
     <workbookView xWindow="240" yWindow="105" windowWidth="28395" windowHeight="12480"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
-    <sheet name="Tabelle3" sheetId="3" r:id="rId3"/>
+    <sheet name="Books" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>Title</t>
   </si>
@@ -42,69 +40,95 @@
     <t>ISBN</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>Writer</t>
   </si>
   <si>
     <t>SeriesNumber</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>한국어</t>
+  </si>
+  <si>
+    <t>BookFormat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2023-10-15</t>
+  </si>
+  <si>
+    <t>2019-07-30</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024-09-30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Location</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>99c47682</t>
+  </si>
+  <si>
+    <t>강아지 시험</t>
+  </si>
+  <si>
+    <t>이묘신</t>
+  </si>
+  <si>
+    <t>이야기 반짝</t>
+  </si>
+  <si>
+    <t>해와나무</t>
+  </si>
+  <si>
+    <t>9788962681857</t>
+  </si>
+  <si>
+    <t>c4a45fb0</t>
+  </si>
+  <si>
+    <t>2024-10-25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>책벌레 공부벌레 일벌레</t>
+  </si>
+  <si>
+    <t>동심원</t>
+  </si>
+  <si>
+    <t>푸른책들</t>
+  </si>
+  <si>
     <t>2024-07-24</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>강아지 시험</t>
-  </si>
-  <si>
-    <t>이묘신</t>
-  </si>
-  <si>
-    <t>책벌레 공부벌레 일벌레</t>
-  </si>
-  <si>
-    <t>c4a45fb0</t>
-  </si>
-  <si>
-    <t>99c47682</t>
-  </si>
-  <si>
-    <t>2019-07-30</t>
-  </si>
-  <si>
-    <t>해와나무</t>
-  </si>
-  <si>
-    <t>한국어</t>
-  </si>
-  <si>
-    <t>이야기 반짝</t>
-  </si>
-  <si>
-    <t>9788962681857</t>
-  </si>
-  <si>
-    <t>강아지를 너무나 키우고 싶어하는 선후가 강아지 키우는 걸 반대하는 엄마를 설득하고, 강아지 시험을 통과하기 위해 공부를 하고, 미나와 함께 강아지 돌보기 실습을 하면서 강아지 키우는 법을 차츰 알아가는 책이다. 이 책은 반려동물이 보기에 예쁘다고 혹은 친구가 키우니까 나도 키우겠다며 반려동물을 무작정 키우자고 조르는 어린이들이 보면 정말 좋은 책이다.</t>
-  </si>
-  <si>
-    <t>동심원</t>
-  </si>
-  <si>
-    <t>푸른책들</t>
-  </si>
-  <si>
     <t>9788957982365</t>
   </si>
   <si>
-    <t>시인은 아이의 눈과 입을 빌어 아빠에게서 배려와 느림의 철학을, 할머니에게서 따뜻한 마음과 자연의 소중함을, 엄마에게서 위로와 격려를, 이모에게서 긍정적인 사고를 이야기한다.</t>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>68e75fa3</t>
   </si>
   <si>
+    <t>2024-10-25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>김정희 할머니 길</t>
   </si>
   <si>
@@ -114,61 +138,31 @@
     <t>초록달팽이</t>
   </si>
   <si>
-    <t>2023-10-15</t>
-  </si>
-  <si>
     <t>9791193400005</t>
   </si>
   <si>
-    <t>초록달팽이에서 처음으로 나온 동화책이다. 그동안 동시, 동화, 그림책 등 여러 장르를 넘나들며 독자들에게 많은 관심과 사랑을 받아 온 이묘신 작가가 자신의 경험을 한 편의 따뜻하고 아름다운 이야기로 꾸몄다."</t>
-  </si>
-  <si>
     <t>f76eb274</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>날아라, 씨앗 폭탄!</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>가로세로그림책</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>초록개구리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2024-05-25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>9791157822973</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>달달숲 마을엔 나무가 없다. 사람들이 모조리 베어 가서 그루터기만 가득하다. 어느 날, 어른 동물들은 ‘폭탄’을 만들기로 한다. 그 소식을 엿들은 아기 여우는 헐레벌떡 친구들에게 달려간다. 아기 동물들은 어른들이 전쟁을 벌일 거라는 생각에 그 ‘폭탄’을 찾아서 꼭꼭 숨긴다. 그런데… 참 이상해하다. 며칠 뒤 ‘폭탄’을 숨긴 곳에 파릇파릇한 싹이 돋아난 것이다. 이 수상한 폭탄의 정체는 무엇일까?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BookFormat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2024-10-25</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2024-09-30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -178,7 +172,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,19 +182,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -220,44 +245,66 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -554,269 +601,243 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="11.375" defaultRowHeight="16.5"/>
+  <dimension ref="A1:T5"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="10.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" style="2" customWidth="1"/>
-    <col min="9" max="9" width="18" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.125" style="8" customWidth="1"/>
-    <col min="13" max="13" width="7.625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="47.25" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="11.375" style="2"/>
+    <col min="1" max="1" width="10.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="46.75" style="7" customWidth="1"/>
+    <col min="4" max="4" width="18.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="6.25" style="6" customWidth="1"/>
+    <col min="8" max="8" width="10.375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10.75" style="4" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="4.875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.875" style="8" customWidth="1"/>
+    <col min="15" max="15" width="11.375" style="3" customWidth="1"/>
+    <col min="16" max="20" width="0" style="3" hidden="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.375" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:14" ht="27">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="33">
+      <c r="A2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="13">
+        <v>5</v>
+      </c>
+      <c r="G2" s="13">
+        <v>80</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="14">
+        <v>0</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="11"/>
+    </row>
+    <row r="3" spans="1:14" ht="33">
+      <c r="A3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="13">
+        <v>9</v>
+      </c>
+      <c r="G3" s="13">
+        <v>64</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="14">
+        <v>0</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" ht="33">
+      <c r="A4" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="13">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G4" s="13">
+        <v>76</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="16">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="M4" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="15"/>
+    </row>
+    <row r="5" spans="1:14" ht="33">
+      <c r="A5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="13">
+        <v>17</v>
+      </c>
+      <c r="G5" s="13">
         <v>44</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="H5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="115.5">
-      <c r="A2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="8">
-        <v>5</v>
-      </c>
-      <c r="G2" s="8">
-        <v>80</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="9">
+      <c r="J5" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="16">
         <v>0</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="66">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="8">
-        <v>9</v>
-      </c>
-      <c r="G3" s="8">
-        <v>64</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="9">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8">
-        <v>76</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="M5" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="10">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="8">
-        <v>17</v>
-      </c>
-      <c r="G5" s="8">
-        <v>44</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="10">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="N5" s="15"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>